--- a/runs/yolo_thermal_v8n_28.05.2026/training_metrics.xlsx
+++ b/runs/yolo_thermal_v8n_28.05.2026/training_metrics.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y29"/>
+  <dimension ref="A1:Y102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2280,6 +2280,4307 @@
       <c r="X29" s="5" t="n"/>
       <c r="Y29" s="5" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>0.00748</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>1.2112</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>1.3354</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0.7517</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0.8092</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0.8794999999999999</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>0.7733</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>0.7936</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>0.7833</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.8141</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>0.5642</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>0.9194</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>0.5051</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>0.8772</v>
+      </c>
+      <c r="Q30" s="4" t="n"/>
+      <c r="R30" s="4" t="n"/>
+      <c r="S30" s="4" t="n"/>
+      <c r="T30" s="4" t="n"/>
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="n"/>
+      <c r="W30" s="4" t="n"/>
+      <c r="X30" s="4" t="n"/>
+      <c r="Y30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0.00739</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1.1641</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>1.3335</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0.5806</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0.7498</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.8349</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0.8791</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0.8451</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0.7451</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0.8147</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>0.5646</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>0.9197</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0.5053</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>0.9256</v>
+      </c>
+      <c r="Q31" s="5" t="n"/>
+      <c r="R31" s="5" t="n"/>
+      <c r="S31" s="5" t="n"/>
+      <c r="T31" s="5" t="n"/>
+      <c r="U31" s="5" t="n"/>
+      <c r="V31" s="5" t="n"/>
+      <c r="W31" s="5" t="n"/>
+      <c r="X31" s="5" t="n"/>
+      <c r="Y31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>1.3604</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>1.3325</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0.6444</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>0.7493</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0.8788</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0.8381999999999999</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>0.7479</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>0.7904</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>0.8155</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>0.9197</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>0.5061</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>0.9249000000000001</v>
+      </c>
+      <c r="Q32" s="4" t="n"/>
+      <c r="R32" s="4" t="n"/>
+      <c r="S32" s="4" t="n"/>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="4" t="n"/>
+      <c r="V32" s="4" t="n"/>
+      <c r="W32" s="4" t="n"/>
+      <c r="X32" s="4" t="n"/>
+      <c r="Y32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0.00721</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1.3314</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0.5623</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.8437</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0.8786</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0.8322000000000001</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0.7884</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>0.8171</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>0.5676</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>0.9201</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>0.9224</v>
+      </c>
+      <c r="Q33" s="5" t="n"/>
+      <c r="R33" s="5" t="n"/>
+      <c r="S33" s="5" t="n"/>
+      <c r="T33" s="5" t="n"/>
+      <c r="U33" s="5" t="n"/>
+      <c r="V33" s="5" t="n"/>
+      <c r="W33" s="5" t="n"/>
+      <c r="X33" s="5" t="n"/>
+      <c r="Y33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>0.00712</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>1.5142</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>1.3298</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0.7266</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>0.7478</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0.9106</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0.8783</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0.7426</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>0.8416</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>0.8151</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>0.5663</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>0.9199000000000001</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>0.5063</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>0.8337</v>
+      </c>
+      <c r="Q34" s="4" t="n"/>
+      <c r="R34" s="4" t="n"/>
+      <c r="S34" s="4" t="n"/>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="n"/>
+      <c r="W34" s="4" t="n"/>
+      <c r="X34" s="4" t="n"/>
+      <c r="Y34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0.00703</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>1.6382</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>1.3283</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.6514</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.7463</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.8386</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0.8781</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0.7482</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0.8404</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0.7917</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>0.8136</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>0.5649</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>0.9195</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0.5067</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0.8371</v>
+      </c>
+      <c r="Q35" s="5" t="n"/>
+      <c r="R35" s="5" t="n"/>
+      <c r="S35" s="5" t="n"/>
+      <c r="T35" s="5" t="n"/>
+      <c r="U35" s="5" t="n"/>
+      <c r="V35" s="5" t="n"/>
+      <c r="W35" s="5" t="n"/>
+      <c r="X35" s="5" t="n"/>
+      <c r="Y35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>0.00694</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>1.3004</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>1.327</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0.7449</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0.8779</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0.7628</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>0.8375</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0.7984</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>0.8137</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>0.9196</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>0.5074</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="Q36" s="4" t="n"/>
+      <c r="R36" s="4" t="n"/>
+      <c r="S36" s="4" t="n"/>
+      <c r="T36" s="4" t="n"/>
+      <c r="U36" s="4" t="n"/>
+      <c r="V36" s="4" t="n"/>
+      <c r="W36" s="4" t="n"/>
+      <c r="X36" s="4" t="n"/>
+      <c r="Y36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0.00685</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>1.2477</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1.3258</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.5929</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.7439</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.8431</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0.8774</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>0.7737000000000001</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>0.8221000000000001</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0.7972</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>0.5609</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>0.9197</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>0.8595</v>
+      </c>
+      <c r="Q37" s="5" t="n"/>
+      <c r="R37" s="5" t="n"/>
+      <c r="S37" s="5" t="n"/>
+      <c r="T37" s="5" t="n"/>
+      <c r="U37" s="5" t="n"/>
+      <c r="V37" s="5" t="n"/>
+      <c r="W37" s="5" t="n"/>
+      <c r="X37" s="5" t="n"/>
+      <c r="Y37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>0.00676</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>1.3621</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>1.3239</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0.7429</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>0.8643</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0.8769</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0.7798</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>0.8018</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0.7906</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>0.5586</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>0.9205</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>0.5085</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>0.8851</v>
+      </c>
+      <c r="Q38" s="4" t="n"/>
+      <c r="R38" s="4" t="n"/>
+      <c r="S38" s="4" t="n"/>
+      <c r="T38" s="4" t="n"/>
+      <c r="U38" s="4" t="n"/>
+      <c r="V38" s="4" t="n"/>
+      <c r="W38" s="4" t="n"/>
+      <c r="X38" s="4" t="n"/>
+      <c r="Y38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0.00667</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>1.3226</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.6172</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.7413</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.9021</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0.8767</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>0.7937</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>0.7824</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>0.8142</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>0.5605</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>0.5092</v>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>0.8981</v>
+      </c>
+      <c r="Q39" s="5" t="n"/>
+      <c r="R39" s="5" t="n"/>
+      <c r="S39" s="5" t="n"/>
+      <c r="T39" s="5" t="n"/>
+      <c r="U39" s="5" t="n"/>
+      <c r="V39" s="5" t="n"/>
+      <c r="W39" s="5" t="n"/>
+      <c r="X39" s="5" t="n"/>
+      <c r="Y39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>0.00658</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>1.2052</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0.6086</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0.7401</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0.8338</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0.8764</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0.8252</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>0.7753</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>0.7995</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>0.8149</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>0.5596</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>0.9216</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>0.5094</v>
+      </c>
+      <c r="P40" s="4" t="n">
+        <v>0.9095</v>
+      </c>
+      <c r="Q40" s="4" t="n"/>
+      <c r="R40" s="4" t="n"/>
+      <c r="S40" s="4" t="n"/>
+      <c r="T40" s="4" t="n"/>
+      <c r="U40" s="4" t="n"/>
+      <c r="V40" s="4" t="n"/>
+      <c r="W40" s="4" t="n"/>
+      <c r="X40" s="4" t="n"/>
+      <c r="Y40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0.00649</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1.3529</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.6532</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.7385</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.8836000000000001</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0.8274</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0.7998</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>0.8154</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>0.9218</v>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0.5091</v>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>0.9116</v>
+      </c>
+      <c r="Q41" s="5" t="n"/>
+      <c r="R41" s="5" t="n"/>
+      <c r="S41" s="5" t="n"/>
+      <c r="T41" s="5" t="n"/>
+      <c r="U41" s="5" t="n"/>
+      <c r="V41" s="5" t="n"/>
+      <c r="W41" s="5" t="n"/>
+      <c r="X41" s="5" t="n"/>
+      <c r="Y41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>1.5651</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>1.3176</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0.7377</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0.8757</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>0.8079</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>0.8005</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0.8041</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>0.8177</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>0.5616</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>0.9224</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>0.5102</v>
+      </c>
+      <c r="P42" s="4" t="n">
+        <v>0.8843</v>
+      </c>
+      <c r="Q42" s="4" t="n"/>
+      <c r="R42" s="4" t="n"/>
+      <c r="S42" s="4" t="n"/>
+      <c r="T42" s="4" t="n"/>
+      <c r="U42" s="4" t="n"/>
+      <c r="V42" s="4" t="n"/>
+      <c r="W42" s="4" t="n"/>
+      <c r="X42" s="4" t="n"/>
+      <c r="Y42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0.00631</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>1.4975</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.7035</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.7367</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.9371</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0.8756</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>0.8076</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>0.7978</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0.8027</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>0.8184</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>0.5637</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>0.5113</v>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>0.8853</v>
+      </c>
+      <c r="Q43" s="5" t="n"/>
+      <c r="R43" s="5" t="n"/>
+      <c r="S43" s="5" t="n"/>
+      <c r="T43" s="5" t="n"/>
+      <c r="U43" s="5" t="n"/>
+      <c r="V43" s="5" t="n"/>
+      <c r="W43" s="5" t="n"/>
+      <c r="X43" s="5" t="n"/>
+      <c r="Y43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>0.00622</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>1.4884</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>1.3155</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0.8397</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>0.8754</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>0.8257</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>0.7701</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>0.7969000000000001</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>0.8194</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>0.5646</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>0.9232</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>0.5124</v>
+      </c>
+      <c r="P44" s="4" t="n">
+        <v>0.9171</v>
+      </c>
+      <c r="Q44" s="4" t="n"/>
+      <c r="R44" s="4" t="n"/>
+      <c r="S44" s="4" t="n"/>
+      <c r="T44" s="4" t="n"/>
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="n"/>
+      <c r="W44" s="4" t="n"/>
+      <c r="X44" s="4" t="n"/>
+      <c r="Y44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0.00613</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>1.4472</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>1.3145</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.6681</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0.7345</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.8988</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0.8751</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>0.7669</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0.7963</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>0.8221000000000001</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>0.9233</v>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>0.9203</v>
+      </c>
+      <c r="Q45" s="5" t="n"/>
+      <c r="R45" s="5" t="n"/>
+      <c r="S45" s="5" t="n"/>
+      <c r="T45" s="5" t="n"/>
+      <c r="U45" s="5" t="n"/>
+      <c r="V45" s="5" t="n"/>
+      <c r="W45" s="5" t="n"/>
+      <c r="X45" s="5" t="n"/>
+      <c r="Y45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>0.00604</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>1.2893</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>1.3136</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0.5919</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0.7332</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>0.7721</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>0.8086</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>0.8236</v>
+      </c>
+      <c r="M46" s="4" t="n">
+        <v>0.5687</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>0.9241</v>
+      </c>
+      <c r="O46" s="4" t="n">
+        <v>0.5142</v>
+      </c>
+      <c r="P46" s="4" t="n">
+        <v>0.8671</v>
+      </c>
+      <c r="Q46" s="4" t="n"/>
+      <c r="R46" s="4" t="n"/>
+      <c r="S46" s="4" t="n"/>
+      <c r="T46" s="4" t="n"/>
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="n"/>
+      <c r="W46" s="4" t="n"/>
+      <c r="X46" s="4" t="n"/>
+      <c r="Y46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0.00595</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>1.4272</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>1.3129</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.7314000000000001</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.8366</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0.8749</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0.7527</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>0.8444</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.7959000000000001</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>0.8276</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0.5706</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>0.9243</v>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>0.5152</v>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>0.8332000000000001</v>
+      </c>
+      <c r="Q47" s="5" t="n"/>
+      <c r="R47" s="5" t="n"/>
+      <c r="S47" s="5" t="n"/>
+      <c r="T47" s="5" t="n"/>
+      <c r="U47" s="5" t="n"/>
+      <c r="V47" s="5" t="n"/>
+      <c r="W47" s="5" t="n"/>
+      <c r="X47" s="5" t="n"/>
+      <c r="Y47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>0.00586</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>1.3394</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>1.3107</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0.6395</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>0.7299</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>0.8944</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>0.8745000000000001</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>0.8151</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>0.8048999999999999</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>0.8283</v>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v>0.5686</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>0.9257</v>
+      </c>
+      <c r="O48" s="4" t="n">
+        <v>0.5163</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>0.8983</v>
+      </c>
+      <c r="Q48" s="4" t="n"/>
+      <c r="R48" s="4" t="n"/>
+      <c r="S48" s="4" t="n"/>
+      <c r="T48" s="4" t="n"/>
+      <c r="U48" s="4" t="n"/>
+      <c r="V48" s="4" t="n"/>
+      <c r="W48" s="4" t="n"/>
+      <c r="X48" s="4" t="n"/>
+      <c r="Y48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0.00577</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>1.5816</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.7289</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.8207</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.8743</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>0.7942</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.8058999999999999</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>0.8285</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>0.5695</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>0.9252</v>
+      </c>
+      <c r="O49" s="5" t="n">
+        <v>0.5171</v>
+      </c>
+      <c r="P49" s="5" t="n">
+        <v>0.9038</v>
+      </c>
+      <c r="Q49" s="5" t="n"/>
+      <c r="R49" s="5" t="n"/>
+      <c r="S49" s="5" t="n"/>
+      <c r="T49" s="5" t="n"/>
+      <c r="U49" s="5" t="n"/>
+      <c r="V49" s="5" t="n"/>
+      <c r="W49" s="5" t="n"/>
+      <c r="X49" s="5" t="n"/>
+      <c r="Y49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>0.00568</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>1.5429</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>1.3086</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0.7111</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0.7275</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>0.8912</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>0.8741</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>0.7411</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>0.8628</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>0.7973</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>0.8280999999999999</v>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>0.5692</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>0.5177</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="Q50" s="4" t="n"/>
+      <c r="R50" s="4" t="n"/>
+      <c r="S50" s="4" t="n"/>
+      <c r="T50" s="4" t="n"/>
+      <c r="U50" s="4" t="n"/>
+      <c r="V50" s="4" t="n"/>
+      <c r="W50" s="4" t="n"/>
+      <c r="X50" s="4" t="n"/>
+      <c r="Y50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>0.00559</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>1.2547</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>1.3066</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.8379</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.8739</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>0.7798</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>0.8233</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0.8008999999999999</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>0.5695</v>
+      </c>
+      <c r="N51" s="5" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="O51" s="5" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="P51" s="5" t="n">
+        <v>0.8699</v>
+      </c>
+      <c r="Q51" s="5" t="n"/>
+      <c r="R51" s="5" t="n"/>
+      <c r="S51" s="5" t="n"/>
+      <c r="T51" s="5" t="n"/>
+      <c r="U51" s="5" t="n"/>
+      <c r="V51" s="5" t="n"/>
+      <c r="W51" s="5" t="n"/>
+      <c r="X51" s="5" t="n"/>
+      <c r="Y51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>1.6402</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>1.3054</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0.7246</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>0.8313</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>0.8735000000000001</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>0.7793</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>0.8227</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>0.8004</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>0.8268</v>
+      </c>
+      <c r="M52" s="4" t="n">
+        <v>0.5701000000000001</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>0.9261</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>0.5184</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>0.8745000000000001</v>
+      </c>
+      <c r="Q52" s="4" t="n"/>
+      <c r="R52" s="4" t="n"/>
+      <c r="S52" s="4" t="n"/>
+      <c r="T52" s="4" t="n"/>
+      <c r="U52" s="4" t="n"/>
+      <c r="V52" s="4" t="n"/>
+      <c r="W52" s="4" t="n"/>
+      <c r="X52" s="4" t="n"/>
+      <c r="Y52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>0.00541</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>1.2642</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>1.3045</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.6311</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0.7239</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>0.8732</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0.7766</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0.7992</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>0.8276</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>0.5753</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>0.9264</v>
+      </c>
+      <c r="O53" s="5" t="n">
+        <v>0.5188</v>
+      </c>
+      <c r="P53" s="5" t="n">
+        <v>0.8739</v>
+      </c>
+      <c r="Q53" s="5" t="n"/>
+      <c r="R53" s="5" t="n"/>
+      <c r="S53" s="5" t="n"/>
+      <c r="T53" s="5" t="n"/>
+      <c r="U53" s="5" t="n"/>
+      <c r="V53" s="5" t="n"/>
+      <c r="W53" s="5" t="n"/>
+      <c r="X53" s="5" t="n"/>
+      <c r="Y53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>0.00532</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>1.4718</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>1.3028</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0.6947</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0.7225</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>0.8729</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>0.8072</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>0.8081</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>0.8289</v>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>0.5738</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>0.9266</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>0.5191</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>0.9008</v>
+      </c>
+      <c r="Q54" s="4" t="n"/>
+      <c r="R54" s="4" t="n"/>
+      <c r="S54" s="4" t="n"/>
+      <c r="T54" s="4" t="n"/>
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="n"/>
+      <c r="W54" s="4" t="n"/>
+      <c r="X54" s="4" t="n"/>
+      <c r="Y54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>1.3278</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>1.3011</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.6599</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.7212</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.8321</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0.8727</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0.8076</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0.8078</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>0.8278</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>0.5747</v>
+      </c>
+      <c r="N55" s="5" t="n">
+        <v>0.9267</v>
+      </c>
+      <c r="O55" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P55" s="5" t="n">
+        <v>0.9021</v>
+      </c>
+      <c r="Q55" s="5" t="n"/>
+      <c r="R55" s="5" t="n"/>
+      <c r="S55" s="5" t="n"/>
+      <c r="T55" s="5" t="n"/>
+      <c r="U55" s="5" t="n"/>
+      <c r="V55" s="5" t="n"/>
+      <c r="W55" s="5" t="n"/>
+      <c r="X55" s="5" t="n"/>
+      <c r="Y55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>0.00514</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>1.0555</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>1.3004</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0.5367</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>0.7195</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>0.8285</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>0.8726</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>0.8094</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>0.8085</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>0.8297</v>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>0.5729</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>0.5207000000000001</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>0.9033</v>
+      </c>
+      <c r="Q56" s="4" t="n"/>
+      <c r="R56" s="4" t="n"/>
+      <c r="S56" s="4" t="n"/>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="n"/>
+      <c r="W56" s="4" t="n"/>
+      <c r="X56" s="4" t="n"/>
+      <c r="Y56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0.00505</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>1.3023</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>1.2997</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.5790999999999999</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0.7192</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.8601</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>0.8723</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>0.8116</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0.8106</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>0.8289</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="N57" s="5" t="n">
+        <v>0.9272</v>
+      </c>
+      <c r="O57" s="5" t="n">
+        <v>0.5213</v>
+      </c>
+      <c r="P57" s="5" t="n">
+        <v>0.9029</v>
+      </c>
+      <c r="Q57" s="5" t="n"/>
+      <c r="R57" s="5" t="n"/>
+      <c r="S57" s="5" t="n"/>
+      <c r="T57" s="5" t="n"/>
+      <c r="U57" s="5" t="n"/>
+      <c r="V57" s="5" t="n"/>
+      <c r="W57" s="5" t="n"/>
+      <c r="X57" s="5" t="n"/>
+      <c r="Y57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>0.00496</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>1.2373</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>1.2982</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>0.6883</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>0.7181</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>0.8119</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <v>0.8095</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>0.8314</v>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v>0.5747</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>0.9278999999999999</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>0.5224</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>0.9081</v>
+      </c>
+      <c r="Q58" s="4" t="n"/>
+      <c r="R58" s="4" t="n"/>
+      <c r="S58" s="4" t="n"/>
+      <c r="T58" s="4" t="n"/>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n"/>
+      <c r="W58" s="4" t="n"/>
+      <c r="X58" s="4" t="n"/>
+      <c r="Y58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>0.00487</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>1.7466</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>1.2965</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0.7672</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0.7169</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.7871</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0.8716</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>0.8135</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>0.8076</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>0.8106</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>0.8300999999999999</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>0.5759</v>
+      </c>
+      <c r="N59" s="5" t="n">
+        <v>0.9301</v>
+      </c>
+      <c r="O59" s="5" t="n">
+        <v>0.5231</v>
+      </c>
+      <c r="P59" s="5" t="n">
+        <v>0.9099</v>
+      </c>
+      <c r="Q59" s="5" t="n"/>
+      <c r="R59" s="5" t="n"/>
+      <c r="S59" s="5" t="n"/>
+      <c r="T59" s="5" t="n"/>
+      <c r="U59" s="5" t="n"/>
+      <c r="V59" s="5" t="n"/>
+      <c r="W59" s="5" t="n"/>
+      <c r="X59" s="5" t="n"/>
+      <c r="Y59" s="5" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>0.00478</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>1.0091</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>1.2955</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>0.5068</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0.7153</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>0.8361</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>0.8712</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>0.8134</v>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>0.8067</v>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>0.8315</v>
+      </c>
+      <c r="M60" s="4" t="n">
+        <v>0.5759</v>
+      </c>
+      <c r="N60" s="4" t="n">
+        <v>0.9298999999999999</v>
+      </c>
+      <c r="O60" s="4" t="n">
+        <v>0.5235</v>
+      </c>
+      <c r="P60" s="4" t="n">
+        <v>0.9103</v>
+      </c>
+      <c r="Q60" s="4" t="n"/>
+      <c r="R60" s="4" t="n"/>
+      <c r="S60" s="4" t="n"/>
+      <c r="T60" s="4" t="n"/>
+      <c r="U60" s="4" t="n"/>
+      <c r="V60" s="4" t="n"/>
+      <c r="W60" s="4" t="n"/>
+      <c r="X60" s="4" t="n"/>
+      <c r="Y60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>0.00469</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>1.1645</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>1.2939</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0.6243</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0.7145</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.8818</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>0.8148</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>0.8055</v>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>0.8101</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>0.8312</v>
+      </c>
+      <c r="M61" s="5" t="n">
+        <v>0.5737</v>
+      </c>
+      <c r="N61" s="5" t="n">
+        <v>0.9305</v>
+      </c>
+      <c r="O61" s="5" t="n">
+        <v>0.5242</v>
+      </c>
+      <c r="P61" s="5" t="n">
+        <v>0.9136</v>
+      </c>
+      <c r="Q61" s="5" t="n"/>
+      <c r="R61" s="5" t="n"/>
+      <c r="S61" s="5" t="n"/>
+      <c r="T61" s="5" t="n"/>
+      <c r="U61" s="5" t="n"/>
+      <c r="V61" s="5" t="n"/>
+      <c r="W61" s="5" t="n"/>
+      <c r="X61" s="5" t="n"/>
+      <c r="Y61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>1.3091</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>1.2937</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>0.7459</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>0.8817</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>0.8709</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>0.8148</v>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>0.8041</v>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>0.8094</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>0.8305</v>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v>0.5733</v>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>0.9308999999999999</v>
+      </c>
+      <c r="O62" s="4" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="P62" s="4" t="n">
+        <v>0.9144</v>
+      </c>
+      <c r="Q62" s="4" t="n"/>
+      <c r="R62" s="4" t="n"/>
+      <c r="S62" s="4" t="n"/>
+      <c r="T62" s="4" t="n"/>
+      <c r="U62" s="4" t="n"/>
+      <c r="V62" s="4" t="n"/>
+      <c r="W62" s="4" t="n"/>
+      <c r="X62" s="4" t="n"/>
+      <c r="Y62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>0.00451</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>1.4616</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>1.2931</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0.7628</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0.7144</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.8401</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>0.8706</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>0.7815</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>0.8155</v>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>0.7982</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>0.8319</v>
+      </c>
+      <c r="M63" s="5" t="n">
+        <v>0.5745</v>
+      </c>
+      <c r="N63" s="5" t="n">
+        <v>0.9314</v>
+      </c>
+      <c r="O63" s="5" t="n">
+        <v>0.5248</v>
+      </c>
+      <c r="P63" s="5" t="n">
+        <v>0.8952</v>
+      </c>
+      <c r="Q63" s="5" t="n"/>
+      <c r="R63" s="5" t="n"/>
+      <c r="S63" s="5" t="n"/>
+      <c r="T63" s="5" t="n"/>
+      <c r="U63" s="5" t="n"/>
+      <c r="V63" s="5" t="n"/>
+      <c r="W63" s="5" t="n"/>
+      <c r="X63" s="5" t="n"/>
+      <c r="Y63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="4" t="n">
+        <v>0.00442</v>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>1.3955</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>1.2922</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>0.6946</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>0.7131</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>0.8487</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>0.8705000000000001</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>0.8163</v>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>0.7999000000000001</v>
+      </c>
+      <c r="K64" s="4" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>0.8322000000000001</v>
+      </c>
+      <c r="M64" s="4" t="n">
+        <v>0.5747</v>
+      </c>
+      <c r="N64" s="4" t="n">
+        <v>0.9311</v>
+      </c>
+      <c r="O64" s="4" t="n">
+        <v>0.5244</v>
+      </c>
+      <c r="P64" s="4" t="n">
+        <v>0.9167999999999999</v>
+      </c>
+      <c r="Q64" s="4" t="n"/>
+      <c r="R64" s="4" t="n"/>
+      <c r="S64" s="4" t="n"/>
+      <c r="T64" s="4" t="n"/>
+      <c r="U64" s="4" t="n"/>
+      <c r="V64" s="4" t="n"/>
+      <c r="W64" s="4" t="n"/>
+      <c r="X64" s="4" t="n"/>
+      <c r="Y64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>0.00433</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1.3289</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>1.2909</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0.6036</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0.7115</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.8319</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0.8703</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>0.8133</v>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>0.7968</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="M65" s="5" t="n">
+        <v>0.5776</v>
+      </c>
+      <c r="N65" s="5" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="O65" s="5" t="n">
+        <v>0.5249</v>
+      </c>
+      <c r="P65" s="5" t="n">
+        <v>0.8965</v>
+      </c>
+      <c r="Q65" s="5" t="n"/>
+      <c r="R65" s="5" t="n"/>
+      <c r="S65" s="5" t="n"/>
+      <c r="T65" s="5" t="n"/>
+      <c r="U65" s="5" t="n"/>
+      <c r="V65" s="5" t="n"/>
+      <c r="W65" s="5" t="n"/>
+      <c r="X65" s="5" t="n"/>
+      <c r="Y65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="4" t="n">
+        <v>0.00424</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>1.1099</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>1.2896</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>0.5338000000000001</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>0.7099</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>0.7845</v>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>0.8118</v>
+      </c>
+      <c r="K66" s="4" t="n">
+        <v>0.7979000000000001</v>
+      </c>
+      <c r="L66" s="4" t="n">
+        <v>0.8323</v>
+      </c>
+      <c r="M66" s="4" t="n">
+        <v>0.5762</v>
+      </c>
+      <c r="N66" s="4" t="n">
+        <v>0.9307</v>
+      </c>
+      <c r="O66" s="4" t="n">
+        <v>0.5259</v>
+      </c>
+      <c r="P66" s="4" t="n">
+        <v>0.9019</v>
+      </c>
+      <c r="Q66" s="4" t="n"/>
+      <c r="R66" s="4" t="n"/>
+      <c r="S66" s="4" t="n"/>
+      <c r="T66" s="4" t="n"/>
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="n"/>
+      <c r="W66" s="4" t="n"/>
+      <c r="X66" s="4" t="n"/>
+      <c r="Y66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>0.00415</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>1.5386</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>1.2883</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0.7336</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0.7095</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.8067</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0.8697</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>0.7838000000000001</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>0.8116</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>0.7975</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>0.8332000000000001</v>
+      </c>
+      <c r="M67" s="5" t="n">
+        <v>0.5766</v>
+      </c>
+      <c r="N67" s="5" t="n">
+        <v>0.9313</v>
+      </c>
+      <c r="O67" s="5" t="n">
+        <v>0.5269</v>
+      </c>
+      <c r="P67" s="5" t="n">
+        <v>0.9028</v>
+      </c>
+      <c r="Q67" s="5" t="n"/>
+      <c r="R67" s="5" t="n"/>
+      <c r="S67" s="5" t="n"/>
+      <c r="T67" s="5" t="n"/>
+      <c r="U67" s="5" t="n"/>
+      <c r="V67" s="5" t="n"/>
+      <c r="W67" s="5" t="n"/>
+      <c r="X67" s="5" t="n"/>
+      <c r="Y67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="4" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>1.4639</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>0.6575</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>0.7081</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>0.8014</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>0.8695000000000001</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>0.7706</v>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v>0.8324</v>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>0.8003</v>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>0.8296</v>
+      </c>
+      <c r="M68" s="4" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="N68" s="4" t="n">
+        <v>0.9311</v>
+      </c>
+      <c r="O68" s="4" t="n">
+        <v>0.5269</v>
+      </c>
+      <c r="P68" s="4" t="n">
+        <v>0.8815</v>
+      </c>
+      <c r="Q68" s="4" t="n"/>
+      <c r="R68" s="4" t="n"/>
+      <c r="S68" s="4" t="n"/>
+      <c r="T68" s="4" t="n"/>
+      <c r="U68" s="4" t="n"/>
+      <c r="V68" s="4" t="n"/>
+      <c r="W68" s="4" t="n"/>
+      <c r="X68" s="4" t="n"/>
+      <c r="Y68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>0.00397</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>1.3152</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>1.2849</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0.5846</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.8619</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>0.8691</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>0.7737000000000001</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>0.8335</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>0.8025</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>0.8287</v>
+      </c>
+      <c r="M69" s="5" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="N69" s="5" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="O69" s="5" t="n">
+        <v>0.5273</v>
+      </c>
+      <c r="P69" s="5" t="n">
+        <v>0.8869</v>
+      </c>
+      <c r="Q69" s="5" t="n"/>
+      <c r="R69" s="5" t="n"/>
+      <c r="S69" s="5" t="n"/>
+      <c r="T69" s="5" t="n"/>
+      <c r="U69" s="5" t="n"/>
+      <c r="V69" s="5" t="n"/>
+      <c r="W69" s="5" t="n"/>
+      <c r="X69" s="5" t="n"/>
+      <c r="Y69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="4" t="n">
+        <v>0.00388</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>1.5992</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>1.2845</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>0.7133</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>0.7059</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>0.8691</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>0.7728</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>0.8323</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>0.8015</v>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>0.8284</v>
+      </c>
+      <c r="M70" s="4" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>0.9311</v>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v>0.5279</v>
+      </c>
+      <c r="P70" s="4" t="n">
+        <v>0.8887</v>
+      </c>
+      <c r="Q70" s="4" t="n"/>
+      <c r="R70" s="4" t="n"/>
+      <c r="S70" s="4" t="n"/>
+      <c r="T70" s="4" t="n"/>
+      <c r="U70" s="4" t="n"/>
+      <c r="V70" s="4" t="n"/>
+      <c r="W70" s="4" t="n"/>
+      <c r="X70" s="4" t="n"/>
+      <c r="Y70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>0.00379</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>1.4637</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>1.2832</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.6984</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0.7053</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>0.7722</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>0.8319</v>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>0.8294</v>
+      </c>
+      <c r="M71" s="5" t="n">
+        <v>0.5770999999999999</v>
+      </c>
+      <c r="N71" s="5" t="n">
+        <v>0.9308999999999999</v>
+      </c>
+      <c r="O71" s="5" t="n">
+        <v>0.5276999999999999</v>
+      </c>
+      <c r="P71" s="5" t="n">
+        <v>0.8887</v>
+      </c>
+      <c r="Q71" s="5" t="n"/>
+      <c r="R71" s="5" t="n"/>
+      <c r="S71" s="5" t="n"/>
+      <c r="T71" s="5" t="n"/>
+      <c r="U71" s="5" t="n"/>
+      <c r="V71" s="5" t="n"/>
+      <c r="W71" s="5" t="n"/>
+      <c r="X71" s="5" t="n"/>
+      <c r="Y71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>1.0525</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>1.2823</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>0.4784</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>0.7047</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>0.8109</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>0.8689</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>0.7731</v>
+      </c>
+      <c r="J72" s="4" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>0.8304</v>
+      </c>
+      <c r="M72" s="4" t="n">
+        <v>0.5778</v>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>0.9312</v>
+      </c>
+      <c r="O72" s="4" t="n">
+        <v>0.5286</v>
+      </c>
+      <c r="P72" s="4" t="n">
+        <v>0.8904</v>
+      </c>
+      <c r="Q72" s="4" t="n"/>
+      <c r="R72" s="4" t="n"/>
+      <c r="S72" s="4" t="n"/>
+      <c r="T72" s="4" t="n"/>
+      <c r="U72" s="4" t="n"/>
+      <c r="V72" s="4" t="n"/>
+      <c r="W72" s="4" t="n"/>
+      <c r="X72" s="4" t="n"/>
+      <c r="Y72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>0.00361</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>1.1668</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>1.2816</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>0.5952</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>0.7039</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.8247</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>0.7728</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>0.8316</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>0.8011</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>0.8324</v>
+      </c>
+      <c r="M73" s="5" t="n">
+        <v>0.5797</v>
+      </c>
+      <c r="N73" s="5" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="O73" s="5" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="P73" s="5" t="n">
+        <v>0.8899</v>
+      </c>
+      <c r="Q73" s="5" t="n"/>
+      <c r="R73" s="5" t="n"/>
+      <c r="S73" s="5" t="n"/>
+      <c r="T73" s="5" t="n"/>
+      <c r="U73" s="5" t="n"/>
+      <c r="V73" s="5" t="n"/>
+      <c r="W73" s="5" t="n"/>
+      <c r="X73" s="5" t="n"/>
+      <c r="Y73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>0.00352</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>1.2849</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>1.2807</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>0.6183</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>0.8688</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>0.7745</v>
+      </c>
+      <c r="J74" s="4" t="n">
+        <v>0.8308</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>0.8017</v>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>0.8318</v>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v>0.5799</v>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>0.9307</v>
+      </c>
+      <c r="O74" s="4" t="n">
+        <v>0.5286999999999999</v>
+      </c>
+      <c r="P74" s="4" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="Q74" s="4" t="n"/>
+      <c r="R74" s="4" t="n"/>
+      <c r="S74" s="4" t="n"/>
+      <c r="T74" s="4" t="n"/>
+      <c r="U74" s="4" t="n"/>
+      <c r="V74" s="4" t="n"/>
+      <c r="W74" s="4" t="n"/>
+      <c r="X74" s="4" t="n"/>
+      <c r="Y74" s="4" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>1.5106</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>1.2808</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>0.6394</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0.7026</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.8123</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>0.8685</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>0.8304</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>0.8313</v>
+      </c>
+      <c r="M75" s="5" t="n">
+        <v>0.5795</v>
+      </c>
+      <c r="N75" s="5" t="n">
+        <v>0.9308</v>
+      </c>
+      <c r="O75" s="5" t="n">
+        <v>0.5286999999999999</v>
+      </c>
+      <c r="P75" s="5" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="Q75" s="5" t="n"/>
+      <c r="R75" s="5" t="n"/>
+      <c r="S75" s="5" t="n"/>
+      <c r="T75" s="5" t="n"/>
+      <c r="U75" s="5" t="n"/>
+      <c r="V75" s="5" t="n"/>
+      <c r="W75" s="5" t="n"/>
+      <c r="X75" s="5" t="n"/>
+      <c r="Y75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="4" t="n">
+        <v>0.00334</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>1.5058</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>1.2804</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>0.7407</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>0.7017</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>0.9273</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>0.8685</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="J76" s="4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K76" s="4" t="n">
+        <v>0.8028999999999999</v>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>0.8316</v>
+      </c>
+      <c r="M76" s="4" t="n">
+        <v>0.5803</v>
+      </c>
+      <c r="N76" s="4" t="n">
+        <v>0.9311</v>
+      </c>
+      <c r="O76" s="4" t="n">
+        <v>0.5289</v>
+      </c>
+      <c r="P76" s="4" t="n">
+        <v>0.8923</v>
+      </c>
+      <c r="Q76" s="4" t="n"/>
+      <c r="R76" s="4" t="n"/>
+      <c r="S76" s="4" t="n"/>
+      <c r="T76" s="4" t="n"/>
+      <c r="U76" s="4" t="n"/>
+      <c r="V76" s="4" t="n"/>
+      <c r="W76" s="4" t="n"/>
+      <c r="X76" s="4" t="n"/>
+      <c r="Y76" s="4" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>0.00325</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>1.434</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>1.2795</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>0.8055</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>0.7008</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.9861</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>0.8683</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>0.7774</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>0.8305</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>0.8031</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>0.8295</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="N77" s="5" t="n">
+        <v>0.9315</v>
+      </c>
+      <c r="O77" s="5" t="n">
+        <v>0.5299</v>
+      </c>
+      <c r="P77" s="5" t="n">
+        <v>0.8903</v>
+      </c>
+      <c r="Q77" s="5" t="n"/>
+      <c r="R77" s="5" t="n"/>
+      <c r="S77" s="5" t="n"/>
+      <c r="T77" s="5" t="n"/>
+      <c r="U77" s="5" t="n"/>
+      <c r="V77" s="5" t="n"/>
+      <c r="W77" s="5" t="n"/>
+      <c r="X77" s="5" t="n"/>
+      <c r="Y77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="4" t="n">
+        <v>0.00316</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>1.3059</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>1.278</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>0.7003</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>0.8177</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>0.8681</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="J78" s="4" t="n">
+        <v>0.8282</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>0.8018</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>0.8270999999999999</v>
+      </c>
+      <c r="M78" s="4" t="n">
+        <v>0.5782</v>
+      </c>
+      <c r="N78" s="4" t="n">
+        <v>0.9317</v>
+      </c>
+      <c r="O78" s="4" t="n">
+        <v>0.5299</v>
+      </c>
+      <c r="P78" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="Q78" s="4" t="n"/>
+      <c r="R78" s="4" t="n"/>
+      <c r="S78" s="4" t="n"/>
+      <c r="T78" s="4" t="n"/>
+      <c r="U78" s="4" t="n"/>
+      <c r="V78" s="4" t="n"/>
+      <c r="W78" s="4" t="n"/>
+      <c r="X78" s="4" t="n"/>
+      <c r="Y78" s="4" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>0.00307</v>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>1.2788</v>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>1.278</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>0.6765</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0.6996</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.8831</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>0.8679</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>0.8005</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>0.8265</v>
+      </c>
+      <c r="M79" s="5" t="n">
+        <v>0.5786</v>
+      </c>
+      <c r="N79" s="5" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="O79" s="5" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="P79" s="5" t="n">
+        <v>0.8898</v>
+      </c>
+      <c r="Q79" s="5" t="n"/>
+      <c r="R79" s="5" t="n"/>
+      <c r="S79" s="5" t="n"/>
+      <c r="T79" s="5" t="n"/>
+      <c r="U79" s="5" t="n"/>
+      <c r="V79" s="5" t="n"/>
+      <c r="W79" s="5" t="n"/>
+      <c r="X79" s="5" t="n"/>
+      <c r="Y79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="4" t="n">
+        <v>0.00298</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>1.4769</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>1.2762</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>0.7196</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>0.6995</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>0.8238</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>0.8676</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>0.7779</v>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v>0.8282</v>
+      </c>
+      <c r="K80" s="4" t="n">
+        <v>0.8023</v>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>0.8262</v>
+      </c>
+      <c r="M80" s="4" t="n">
+        <v>0.5785</v>
+      </c>
+      <c r="N80" s="4" t="n">
+        <v>0.9326</v>
+      </c>
+      <c r="O80" s="4" t="n">
+        <v>0.5318000000000001</v>
+      </c>
+      <c r="P80" s="4" t="n">
+        <v>0.8905</v>
+      </c>
+      <c r="Q80" s="4" t="n"/>
+      <c r="R80" s="4" t="n"/>
+      <c r="S80" s="4" t="n"/>
+      <c r="T80" s="4" t="n"/>
+      <c r="U80" s="4" t="n"/>
+      <c r="V80" s="4" t="n"/>
+      <c r="W80" s="4" t="n"/>
+      <c r="X80" s="4" t="n"/>
+      <c r="Y80" s="4" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>0.00289</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>1.4692</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>1.276</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>0.6423</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.8021</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>0.8673999999999999</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>0.7743</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>0.8304</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>0.8014</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>0.8264</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>0.5788</v>
+      </c>
+      <c r="N81" s="5" t="n">
+        <v>0.9327</v>
+      </c>
+      <c r="O81" s="5" t="n">
+        <v>0.5318000000000001</v>
+      </c>
+      <c r="P81" s="5" t="n">
+        <v>0.8894</v>
+      </c>
+      <c r="Q81" s="5" t="n"/>
+      <c r="R81" s="5" t="n"/>
+      <c r="S81" s="5" t="n"/>
+      <c r="T81" s="5" t="n"/>
+      <c r="U81" s="5" t="n"/>
+      <c r="V81" s="5" t="n"/>
+      <c r="W81" s="5" t="n"/>
+      <c r="X81" s="5" t="n"/>
+      <c r="Y81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="4" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>1.0761</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>1.2742</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>0.4987</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>0.6982</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>0.8671</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>0.7582</v>
+      </c>
+      <c r="J82" s="4" t="n">
+        <v>0.8357</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>0.7951</v>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>0.8255</v>
+      </c>
+      <c r="M82" s="4" t="n">
+        <v>0.5778</v>
+      </c>
+      <c r="N82" s="4" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="O82" s="4" t="n">
+        <v>0.5328000000000001</v>
+      </c>
+      <c r="P82" s="4" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="Q82" s="4" t="n"/>
+      <c r="R82" s="4" t="n"/>
+      <c r="S82" s="4" t="n"/>
+      <c r="T82" s="4" t="n"/>
+      <c r="U82" s="4" t="n"/>
+      <c r="V82" s="4" t="n"/>
+      <c r="W82" s="4" t="n"/>
+      <c r="X82" s="4" t="n"/>
+      <c r="Y82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>0.00271</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>1.8118</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>1.2741</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>0.9022</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>0.8668</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>0.7592</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>0.8357</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>0.7956</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>0.5787</v>
+      </c>
+      <c r="N83" s="5" t="n">
+        <v>0.9332</v>
+      </c>
+      <c r="O83" s="5" t="n">
+        <v>0.5332</v>
+      </c>
+      <c r="P83" s="5" t="n">
+        <v>0.8718</v>
+      </c>
+      <c r="Q83" s="5" t="n"/>
+      <c r="R83" s="5" t="n"/>
+      <c r="S83" s="5" t="n"/>
+      <c r="T83" s="5" t="n"/>
+      <c r="U83" s="5" t="n"/>
+      <c r="V83" s="5" t="n"/>
+      <c r="W83" s="5" t="n"/>
+      <c r="X83" s="5" t="n"/>
+      <c r="Y83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="4" t="n">
+        <v>0.00262</v>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>1.4193</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>1.2729</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>0.7245</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>0.6972</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>0.8273</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>0.7579</v>
+      </c>
+      <c r="J84" s="4" t="n">
+        <v>0.8352000000000001</v>
+      </c>
+      <c r="K84" s="4" t="n">
+        <v>0.7947</v>
+      </c>
+      <c r="L84" s="4" t="n">
+        <v>0.8244</v>
+      </c>
+      <c r="M84" s="4" t="n">
+        <v>0.5776</v>
+      </c>
+      <c r="N84" s="4" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="O84" s="4" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="P84" s="4" t="n">
+        <v>0.8687</v>
+      </c>
+      <c r="Q84" s="4" t="n"/>
+      <c r="R84" s="4" t="n"/>
+      <c r="S84" s="4" t="n"/>
+      <c r="T84" s="4" t="n"/>
+      <c r="U84" s="4" t="n"/>
+      <c r="V84" s="4" t="n"/>
+      <c r="W84" s="4" t="n"/>
+      <c r="X84" s="4" t="n"/>
+      <c r="Y84" s="4" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>0.00253</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>1.3018</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>1.2723</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0.5651</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.6963</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.7963</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>0.8666</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>0.7564</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>0.8336</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>0.7931</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>0.8262</v>
+      </c>
+      <c r="M85" s="5" t="n">
+        <v>0.5796</v>
+      </c>
+      <c r="N85" s="5" t="n">
+        <v>0.9336</v>
+      </c>
+      <c r="O85" s="5" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="P85" s="5" t="n">
+        <v>0.8657</v>
+      </c>
+      <c r="Q85" s="5" t="n"/>
+      <c r="R85" s="5" t="n"/>
+      <c r="S85" s="5" t="n"/>
+      <c r="T85" s="5" t="n"/>
+      <c r="U85" s="5" t="n"/>
+      <c r="V85" s="5" t="n"/>
+      <c r="W85" s="5" t="n"/>
+      <c r="X85" s="5" t="n"/>
+      <c r="Y85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="4" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>1.3478</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>1.2722</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>0.6384</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>0.6955</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>0.8105</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>0.8665</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>0.7593</v>
+      </c>
+      <c r="J86" s="4" t="n">
+        <v>0.8343</v>
+      </c>
+      <c r="K86" s="4" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>0.8260999999999999</v>
+      </c>
+      <c r="M86" s="4" t="n">
+        <v>0.5799</v>
+      </c>
+      <c r="N86" s="4" t="n">
+        <v>0.9336</v>
+      </c>
+      <c r="O86" s="4" t="n">
+        <v>0.5342</v>
+      </c>
+      <c r="P86" s="4" t="n">
+        <v>0.8698</v>
+      </c>
+      <c r="Q86" s="4" t="n"/>
+      <c r="R86" s="4" t="n"/>
+      <c r="S86" s="4" t="n"/>
+      <c r="T86" s="4" t="n"/>
+      <c r="U86" s="4" t="n"/>
+      <c r="V86" s="4" t="n"/>
+      <c r="W86" s="4" t="n"/>
+      <c r="X86" s="4" t="n"/>
+      <c r="Y86" s="4" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>1.2816</v>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>1.2712</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0.6165</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.6946</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>0.8663</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>0.7569</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>0.8332000000000001</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>0.7932</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>0.8313</v>
+      </c>
+      <c r="M87" s="5" t="n">
+        <v>0.5815</v>
+      </c>
+      <c r="N87" s="5" t="n">
+        <v>0.9338</v>
+      </c>
+      <c r="O87" s="5" t="n">
+        <v>0.5341</v>
+      </c>
+      <c r="P87" s="5" t="n">
+        <v>0.8663</v>
+      </c>
+      <c r="Q87" s="5" t="n"/>
+      <c r="R87" s="5" t="n"/>
+      <c r="S87" s="5" t="n"/>
+      <c r="T87" s="5" t="n"/>
+      <c r="U87" s="5" t="n"/>
+      <c r="V87" s="5" t="n"/>
+      <c r="W87" s="5" t="n"/>
+      <c r="X87" s="5" t="n"/>
+      <c r="Y87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="4" t="n">
+        <v>0.00226</v>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>1.4706</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>1.2702</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>0.6933</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>0.8661</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>0.7508</v>
+      </c>
+      <c r="J88" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K88" s="4" t="n">
+        <v>0.7929</v>
+      </c>
+      <c r="L88" s="4" t="n">
+        <v>0.8324</v>
+      </c>
+      <c r="M88" s="4" t="n">
+        <v>0.5823</v>
+      </c>
+      <c r="N88" s="4" t="n">
+        <v>0.9347</v>
+      </c>
+      <c r="O88" s="4" t="n">
+        <v>0.5345</v>
+      </c>
+      <c r="P88" s="4" t="n">
+        <v>0.8497</v>
+      </c>
+      <c r="Q88" s="4" t="n"/>
+      <c r="R88" s="4" t="n"/>
+      <c r="S88" s="4" t="n"/>
+      <c r="T88" s="4" t="n"/>
+      <c r="U88" s="4" t="n"/>
+      <c r="V88" s="4" t="n"/>
+      <c r="W88" s="4" t="n"/>
+      <c r="X88" s="4" t="n"/>
+      <c r="Y88" s="4" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>0.00217</v>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>1.3574</v>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>1.2697</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>0.6311</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.6927</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.8048</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>0.7576000000000001</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>0.8334</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>0.7937</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M89" s="5" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="N89" s="5" t="n">
+        <v>0.9348</v>
+      </c>
+      <c r="O89" s="5" t="n">
+        <v>0.5353</v>
+      </c>
+      <c r="P89" s="5" t="n">
+        <v>0.8663999999999999</v>
+      </c>
+      <c r="Q89" s="5" t="n"/>
+      <c r="R89" s="5" t="n"/>
+      <c r="S89" s="5" t="n"/>
+      <c r="T89" s="5" t="n"/>
+      <c r="U89" s="5" t="n"/>
+      <c r="V89" s="5" t="n"/>
+      <c r="W89" s="5" t="n"/>
+      <c r="X89" s="5" t="n"/>
+      <c r="Y89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="4" t="n">
+        <v>0.00208</v>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>1.3129</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>1.2689</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>0.5481</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>0.6922</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>0.8473000000000001</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>0.8659</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>0.7576000000000001</v>
+      </c>
+      <c r="J90" s="4" t="n">
+        <v>0.8338</v>
+      </c>
+      <c r="K90" s="4" t="n">
+        <v>0.7939000000000001</v>
+      </c>
+      <c r="L90" s="4" t="n">
+        <v>0.8323</v>
+      </c>
+      <c r="M90" s="4" t="n">
+        <v>0.5836</v>
+      </c>
+      <c r="N90" s="4" t="n">
+        <v>0.9342</v>
+      </c>
+      <c r="O90" s="4" t="n">
+        <v>0.5353</v>
+      </c>
+      <c r="P90" s="4" t="n">
+        <v>0.8651</v>
+      </c>
+      <c r="Q90" s="4" t="n"/>
+      <c r="R90" s="4" t="n"/>
+      <c r="S90" s="4" t="n"/>
+      <c r="T90" s="4" t="n"/>
+      <c r="U90" s="4" t="n"/>
+      <c r="V90" s="4" t="n"/>
+      <c r="W90" s="4" t="n"/>
+      <c r="X90" s="4" t="n"/>
+      <c r="Y90" s="4" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>0.00199</v>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>1.2045</v>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>1.2687</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>0.5168</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>0.6915</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.8043</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>0.8657</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>0.7556</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>0.8332000000000001</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>0.7925</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="M91" s="5" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="N91" s="5" t="n">
+        <v>0.9347</v>
+      </c>
+      <c r="O91" s="5" t="n">
+        <v>0.5356</v>
+      </c>
+      <c r="P91" s="5" t="n">
+        <v>0.8624000000000001</v>
+      </c>
+      <c r="Q91" s="5" t="n"/>
+      <c r="R91" s="5" t="n"/>
+      <c r="S91" s="5" t="n"/>
+      <c r="T91" s="5" t="n"/>
+      <c r="U91" s="5" t="n"/>
+      <c r="V91" s="5" t="n"/>
+      <c r="W91" s="5" t="n"/>
+      <c r="X91" s="5" t="n"/>
+      <c r="Y91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="4" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>1.3237</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>1.2675</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>0.7173</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>0.6915</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>0.8355</v>
+      </c>
+      <c r="H92" s="4" t="n">
+        <v>0.8656</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>0.8288</v>
+      </c>
+      <c r="J92" s="4" t="n">
+        <v>0.7727000000000001</v>
+      </c>
+      <c r="K92" s="4" t="n">
+        <v>0.7998</v>
+      </c>
+      <c r="L92" s="4" t="n">
+        <v>0.8339</v>
+      </c>
+      <c r="M92" s="4" t="n">
+        <v>0.5846</v>
+      </c>
+      <c r="N92" s="4" t="n">
+        <v>0.9349</v>
+      </c>
+      <c r="O92" s="4" t="n">
+        <v>0.5363</v>
+      </c>
+      <c r="P92" s="4" t="n">
+        <v>0.9378</v>
+      </c>
+      <c r="Q92" s="4" t="n"/>
+      <c r="R92" s="4" t="n"/>
+      <c r="S92" s="4" t="n"/>
+      <c r="T92" s="4" t="n"/>
+      <c r="U92" s="4" t="n"/>
+      <c r="V92" s="4" t="n"/>
+      <c r="W92" s="4" t="n"/>
+      <c r="X92" s="4" t="n"/>
+      <c r="Y92" s="4" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>0.00181</v>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>1.0165</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>1.2657</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>0.5006</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>0.6904</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.8376</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>0.8653999999999999</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0.8309</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>0.7712</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>0.7999000000000001</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>0.8335</v>
+      </c>
+      <c r="M93" s="5" t="n">
+        <v>0.5844</v>
+      </c>
+      <c r="N93" s="5" t="n">
+        <v>0.9347</v>
+      </c>
+      <c r="O93" s="5" t="n">
+        <v>0.5364</v>
+      </c>
+      <c r="P93" s="5" t="n">
+        <v>0.9407</v>
+      </c>
+      <c r="Q93" s="5" t="n"/>
+      <c r="R93" s="5" t="n"/>
+      <c r="S93" s="5" t="n"/>
+      <c r="T93" s="5" t="n"/>
+      <c r="U93" s="5" t="n"/>
+      <c r="V93" s="5" t="n"/>
+      <c r="W93" s="5" t="n"/>
+      <c r="X93" s="5" t="n"/>
+      <c r="Y93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="4" t="n">
+        <v>0.00172</v>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>0.9368</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>1.2649</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>0.4696</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>0.6891</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>0.8217</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>0.8652</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>0.8297</v>
+      </c>
+      <c r="J94" s="4" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K94" s="4" t="n">
+        <v>0.8008999999999999</v>
+      </c>
+      <c r="L94" s="4" t="n">
+        <v>0.8349</v>
+      </c>
+      <c r="M94" s="4" t="n">
+        <v>0.5858</v>
+      </c>
+      <c r="N94" s="4" t="n">
+        <v>0.9354</v>
+      </c>
+      <c r="O94" s="4" t="n">
+        <v>0.5376</v>
+      </c>
+      <c r="P94" s="4" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="Q94" s="4" t="n"/>
+      <c r="R94" s="4" t="n"/>
+      <c r="S94" s="4" t="n"/>
+      <c r="T94" s="4" t="n"/>
+      <c r="U94" s="4" t="n"/>
+      <c r="V94" s="4" t="n"/>
+      <c r="W94" s="4" t="n"/>
+      <c r="X94" s="4" t="n"/>
+      <c r="Y94" s="4" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>0.00163</v>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>0.8858</v>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>1.2646</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>0.4319</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>0.6883</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>0.8651</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>0.8343</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>0.7732</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>0.8026</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>0.8351</v>
+      </c>
+      <c r="M95" s="5" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="N95" s="5" t="n">
+        <v>0.9356</v>
+      </c>
+      <c r="O95" s="5" t="n">
+        <v>0.5379</v>
+      </c>
+      <c r="P95" s="5" t="n">
+        <v>0.9381</v>
+      </c>
+      <c r="Q95" s="5" t="n"/>
+      <c r="R95" s="5" t="n"/>
+      <c r="S95" s="5" t="n"/>
+      <c r="T95" s="5" t="n"/>
+      <c r="U95" s="5" t="n"/>
+      <c r="V95" s="5" t="n"/>
+      <c r="W95" s="5" t="n"/>
+      <c r="X95" s="5" t="n"/>
+      <c r="Y95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="4" t="n">
+        <v>0.00154</v>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>1.3637</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>1.2629</v>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>0.6601</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>0.6872</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>0.8581</v>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>0.8648</v>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>0.7583</v>
+      </c>
+      <c r="J96" s="4" t="n">
+        <v>0.8451</v>
+      </c>
+      <c r="K96" s="4" t="n">
+        <v>0.7994</v>
+      </c>
+      <c r="L96" s="4" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="M96" s="4" t="n">
+        <v>0.5872000000000001</v>
+      </c>
+      <c r="N96" s="4" t="n">
+        <v>0.9359</v>
+      </c>
+      <c r="O96" s="4" t="n">
+        <v>0.5384</v>
+      </c>
+      <c r="P96" s="4" t="n">
+        <v>0.8594000000000001</v>
+      </c>
+      <c r="Q96" s="4" t="n"/>
+      <c r="R96" s="4" t="n"/>
+      <c r="S96" s="4" t="n"/>
+      <c r="T96" s="4" t="n"/>
+      <c r="U96" s="4" t="n"/>
+      <c r="V96" s="4" t="n"/>
+      <c r="W96" s="4" t="n"/>
+      <c r="X96" s="4" t="n"/>
+      <c r="Y96" s="4" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>0.00145</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>1.0461</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>1.2609</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>0.5169</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0.6868</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.8321</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>0.8646</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>0.7587</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>0.8007</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>0.8349</v>
+      </c>
+      <c r="M97" s="5" t="n">
+        <v>0.5901</v>
+      </c>
+      <c r="N97" s="5" t="n">
+        <v>0.9365</v>
+      </c>
+      <c r="O97" s="5" t="n">
+        <v>0.5387999999999999</v>
+      </c>
+      <c r="P97" s="5" t="n">
+        <v>0.8595</v>
+      </c>
+      <c r="Q97" s="5" t="n"/>
+      <c r="R97" s="5" t="n"/>
+      <c r="S97" s="5" t="n"/>
+      <c r="T97" s="5" t="n"/>
+      <c r="U97" s="5" t="n"/>
+      <c r="V97" s="5" t="n"/>
+      <c r="W97" s="5" t="n"/>
+      <c r="X97" s="5" t="n"/>
+      <c r="Y97" s="5" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="4" t="n">
+        <v>0.00136</v>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>1.3053</v>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>1.2598</v>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>0.5812</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>0.6856</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0.8288</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0.8643999999999999</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>0.7594</v>
+      </c>
+      <c r="J98" s="4" t="n">
+        <v>0.8474</v>
+      </c>
+      <c r="K98" s="4" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="L98" s="4" t="n">
+        <v>0.8356</v>
+      </c>
+      <c r="M98" s="4" t="n">
+        <v>0.5886</v>
+      </c>
+      <c r="N98" s="4" t="n">
+        <v>0.9368</v>
+      </c>
+      <c r="O98" s="4" t="n">
+        <v>0.5387999999999999</v>
+      </c>
+      <c r="P98" s="4" t="n">
+        <v>0.8601</v>
+      </c>
+      <c r="Q98" s="4" t="n"/>
+      <c r="R98" s="4" t="n"/>
+      <c r="S98" s="4" t="n"/>
+      <c r="T98" s="4" t="n"/>
+      <c r="U98" s="4" t="n"/>
+      <c r="V98" s="4" t="n"/>
+      <c r="W98" s="4" t="n"/>
+      <c r="X98" s="4" t="n"/>
+      <c r="Y98" s="4" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>0.00127</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>1.1973</v>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>1.2584</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>0.6847</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.8364</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>0.8643</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>0.7602</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>0.8468</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>0.8011</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>0.8353</v>
+      </c>
+      <c r="M99" s="5" t="n">
+        <v>0.5891999999999999</v>
+      </c>
+      <c r="N99" s="5" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="O99" s="5" t="n">
+        <v>0.5397999999999999</v>
+      </c>
+      <c r="P99" s="5" t="n">
+        <v>0.8627</v>
+      </c>
+      <c r="Q99" s="5" t="n"/>
+      <c r="R99" s="5" t="n"/>
+      <c r="S99" s="5" t="n"/>
+      <c r="T99" s="5" t="n"/>
+      <c r="U99" s="5" t="n"/>
+      <c r="V99" s="5" t="n"/>
+      <c r="W99" s="5" t="n"/>
+      <c r="X99" s="5" t="n"/>
+      <c r="Y99" s="5" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="4" t="n">
+        <v>0.00118</v>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>1.2393</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>1.2574</v>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>0.5309</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>0.6842</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>0.8447</v>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>0.8642</v>
+      </c>
+      <c r="I100" s="4" t="n">
+        <v>0.7605</v>
+      </c>
+      <c r="J100" s="4" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="K100" s="4" t="n">
+        <v>0.8023</v>
+      </c>
+      <c r="L100" s="4" t="n">
+        <v>0.8353</v>
+      </c>
+      <c r="M100" s="4" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="N100" s="4" t="n">
+        <v>0.9372</v>
+      </c>
+      <c r="O100" s="4" t="n">
+        <v>0.5399</v>
+      </c>
+      <c r="P100" s="4" t="n">
+        <v>0.8622</v>
+      </c>
+      <c r="Q100" s="4" t="n"/>
+      <c r="R100" s="4" t="n"/>
+      <c r="S100" s="4" t="n"/>
+      <c r="T100" s="4" t="n"/>
+      <c r="U100" s="4" t="n"/>
+      <c r="V100" s="4" t="n"/>
+      <c r="W100" s="4" t="n"/>
+      <c r="X100" s="4" t="n"/>
+      <c r="Y100" s="4" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>0.00109</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>1.1209</v>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>1.2569</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>0.5183</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0.6837</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.7892</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>0.8639</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>0.7527</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>0.8525</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>0.7995</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>0.8347</v>
+      </c>
+      <c r="M101" s="5" t="n">
+        <v>0.5889</v>
+      </c>
+      <c r="N101" s="5" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="O101" s="5" t="n">
+        <v>0.5405</v>
+      </c>
+      <c r="P101" s="5" t="n">
+        <v>0.8606</v>
+      </c>
+      <c r="Q101" s="5" t="n"/>
+      <c r="R101" s="5" t="n"/>
+      <c r="S101" s="5" t="n"/>
+      <c r="T101" s="5" t="n"/>
+      <c r="U101" s="5" t="n"/>
+      <c r="V101" s="5" t="n"/>
+      <c r="W101" s="5" t="n"/>
+      <c r="X101" s="5" t="n"/>
+      <c r="Y101" s="5" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" s="4" t="n">
+        <v>0.00109</v>
+      </c>
+      <c r="C102" s="4" t="n">
+        <v>1.1209</v>
+      </c>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="4" t="n">
+        <v>0.5183</v>
+      </c>
+      <c r="F102" s="4" t="n"/>
+      <c r="G102" s="4" t="n">
+        <v>0.7892</v>
+      </c>
+      <c r="H102" s="4" t="n"/>
+      <c r="I102" s="4" t="n">
+        <v>0.7583</v>
+      </c>
+      <c r="J102" s="4" t="n">
+        <v>0.8482</v>
+      </c>
+      <c r="K102" s="4" t="n">
+        <v>0.8008</v>
+      </c>
+      <c r="L102" s="4" t="n">
+        <v>0.8352000000000001</v>
+      </c>
+      <c r="M102" s="4" t="n">
+        <v>0.5899</v>
+      </c>
+      <c r="N102" s="4" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="O102" s="4" t="n">
+        <v>0.5389</v>
+      </c>
+      <c r="P102" s="4" t="n">
+        <v>0.8582</v>
+      </c>
+      <c r="Q102" s="4" t="n"/>
+      <c r="R102" s="4" t="n"/>
+      <c r="S102" s="4" t="n"/>
+      <c r="T102" s="4" t="n"/>
+      <c r="U102" s="4" t="n"/>
+      <c r="V102" s="4" t="n"/>
+      <c r="W102" s="4" t="n"/>
+      <c r="X102" s="4" t="n"/>
+      <c r="Y102" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
